--- a/05_ai-policy-architecture/exercises/solution/ai_aup.xlsx
+++ b/05_ai-policy-architecture/exercises/solution/ai_aup.xlsx
@@ -600,7 +600,7 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Draft a complete, enforceable AI AUP across six sheets (AUP Body, Prohibited Uses, Acceptable Uses, Exception Procedure, Control Map). Pre-filled rows on every sheet show the worked pattern. Cross-reference the Policy Stack Reference sheet (read-only) for out-of-scope cases.</t>
+          <t>Draft a complete, enforceable AI AUP across six working sheets (AUP Body, Prohibited Uses, Acceptable Uses, Exception Procedure, Control Map, Policy Stack Reference — last sheet is read-only). Pre-filled rows on every sheet show the worked pattern. Cross-reference the Policy Stack Reference sheet (read-only) for out-of-scope cases.</t>
         </is>
       </c>
     </row>
